--- a/data/trans_orig/P43C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2007</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2007 (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222314</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206497</t>
+          <t>205579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235625</t>
+          <t>236754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>222314</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>206497</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>235625</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>73,62%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>78,03%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79669</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65229</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66358</t>
+          <t>65229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95486</t>
+          <t>96404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>79669</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>66358</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>95486</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>294</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301983</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>301983</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>301983</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>301983</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248606</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>228930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>228930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>264427</t>
+          <t>265036</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>248606</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>230000</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>264427</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>72,04%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118445</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102624</t>
+          <t>102015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137051</t>
+          <t>138121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>118445</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>102624</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>137051</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>27,96%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367051</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367051</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>367051</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>367051</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>367051</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109319</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96894</t>
+          <t>95997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119727</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>109319</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>96894</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>119727</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>65,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>57,75%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>71,36%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58463</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71785</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>46859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70888</t>
+          <t>71785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>58463</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>48055</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>70888</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>28,64%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>42,25%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>391</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>400973</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>374037</t>
+          <t>375226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>424802</t>
+          <t>429768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>400973</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>374037</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>424802</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>59,93%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>297</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307801</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>279006</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283972</t>
+          <t>279006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334737</t>
+          <t>333548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>307801</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>283972</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>334737</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>40,07%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>688</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>708774</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>708774</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>708774</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>708774</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>708774</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>708774</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311915</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>335628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287570</t>
+          <t>285961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>334446</t>
+          <t>335628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>311915</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>287570</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>334446</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>55,76%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>51,4%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>59,78%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>231</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247521</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224990</t>
+          <t>223808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>271866</t>
+          <t>273475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>247521</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>224990</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>271866</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>48,6%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>530</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559436</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559436</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>559436</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>559436</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>559436</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2438,37 +1853,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>496149</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>463813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>533547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>461470</t>
+          <t>463813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>530471</t>
+          <t>533547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>496149</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>461470</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>530471</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>40,64%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>43,45%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -2551,37 +1931,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>724</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724801</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>687403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>690479</t>
+          <t>687403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>759480</t>
+          <t>757137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>724801</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>690479</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>759480</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>59,36%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>62,2%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -2664,37 +2009,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1220950</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1220950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1220950</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2728,41 +2073,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1220950</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1220950</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1220950</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2781,37 +2091,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1789276</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1735153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1849331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1728245</t>
+          <t>1735153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1843654</t>
+          <t>1849331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1789276</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1728245</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1843654</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>51,96%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>55,43%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -2894,37 +2169,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1536701</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1476646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1590824</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1482323</t>
+          <t>1476646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1597732</t>
+          <t>1590824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1536701</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1482323</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1597732</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>44,57%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>48,04%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -3007,37 +2247,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3325977</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3325977</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3325977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3071,41 +2311,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3246</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3325977</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3325977</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3325977</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3119,7 +2324,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3127,7 +2332,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3142,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3161,25 +2365,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2012</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2012 (tasa de respuesta: 98,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +2387,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3199,17 +2396,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3280,41 +2466,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3337,13 +2488,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3358,37 +2502,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255926</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>268988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>240085</t>
+          <t>240681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269163</t>
+          <t>268988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,47 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>255926</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>240085</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>269163</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>85,86%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -3471,37 +2580,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57559</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44322</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73400</t>
+          <t>72804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,47 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>57559</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>44322</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>73400</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -3584,37 +2658,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313485</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3648,41 +2722,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>313485</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>313485</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>313485</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3701,37 +2740,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>242</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271931</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285182</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256874</t>
+          <t>256716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>285373</t>
+          <t>285182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,47 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>271931</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>256874</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>285373</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>81,76%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>77,23%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -3814,37 +2818,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60668</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47226</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75725</t>
+          <t>75883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,47 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>60668</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>47226</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>75725</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3927,37 +2896,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332599</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332599</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3991,41 +2960,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>332599</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>332599</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>332599</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4044,37 +2978,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>175641</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159921</t>
+          <t>159825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189818</t>
+          <t>189309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,47 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>175641</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>159921</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>189818</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>68,34%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>62,23%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>73,86%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -4157,37 +3056,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81358</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67181</t>
+          <t>67690</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97078</t>
+          <t>97174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,47 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>81358</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>67181</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>97078</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>37,77%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -4270,37 +3134,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256999</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256999</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4334,41 +3198,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>256999</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>256999</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>256999</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4387,37 +3216,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>509</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551897</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>574476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>522626</t>
+          <t>524173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>573790</t>
+          <t>574476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,47 +3276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>551897</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>522626</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>573790</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>72,47%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>68,63%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>75,34%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -4500,37 +3294,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>197</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209666</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187773</t>
+          <t>187087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>238937</t>
+          <t>237390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,47 +3354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>209666</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>187773</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>238937</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>27,53%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>31,37%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -4613,37 +3372,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>706</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>761563</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>761563</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>761563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4677,41 +3436,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>761563</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>761563</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>761563</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4730,37 +3454,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>443</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>482176</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>454535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>507809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>456297</t>
+          <t>454535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>509666</t>
+          <t>507809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,47 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>482176</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>456297</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>509666</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>60,49%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>67,57%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3532,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>272130</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>246497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>299771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244640</t>
+          <t>246497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298009</t>
+          <t>299771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,47 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>272130</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>244640</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>298009</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>32,43%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -4956,37 +3610,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>696</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754306</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754306</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754306</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5020,41 +3674,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>754306</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>754306</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>754306</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5073,37 +3692,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551209</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>516563</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>582654</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>516583</t>
+          <t>516563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>584606</t>
+          <t>582654</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,47 +3752,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>551209</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>516583</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>584606</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>50,28%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>47,13%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>53,33%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3770,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>518</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>544978</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>579624</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>511581</t>
+          <t>513533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>579604</t>
+          <t>579624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,47 +3830,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>544978</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>511581</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>579604</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>49,72%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>46,67%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>52,87%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -5299,37 +3848,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1096187</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1096187</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1096187</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5363,41 +3912,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1096187</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1096187</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1096187</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5416,37 +3930,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2288781</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2225757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2341574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2227223</t>
+          <t>2225757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2343672</t>
+          <t>2341574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,47 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2288781</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2227223</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2343672</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>63,36%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>66,67%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4008,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1226359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1173566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1289383</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1171468</t>
+          <t>1173566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1287917</t>
+          <t>1289383</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,47 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1226359</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1171468</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1287917</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>36,64%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -5642,37 +4086,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3515140</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3515140</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3515140</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5706,41 +4150,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3515140</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3515140</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3515140</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5754,7 +4163,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5762,7 +4171,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -5777,7 +4185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5796,25 +4204,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2016</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2016 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +4226,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5834,17 +4235,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5915,41 +4305,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5972,13 +4327,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5993,37 +4341,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>258</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271170</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255426</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254423</t>
+          <t>255426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284825</t>
+          <t>285371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,47 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>271170</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>254423</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>284825</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>78,96%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>74,08%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>82,94%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -6106,37 +4419,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72260</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58605</t>
+          <t>58059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>88004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,47 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>72260</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>58605</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>89007</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -6219,37 +4497,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343430</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343430</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6283,41 +4561,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>343430</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>343430</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>343430</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6336,37 +4579,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>286</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301605</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285624</t>
+          <t>284941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316623</t>
+          <t>316335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,47 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>301605</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>285624</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>316623</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>77,13%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>85,51%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -6449,37 +4657,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53957</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>53957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84668</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,47 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>68687</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>53669</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>84668</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -6562,37 +4735,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370292</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6626,41 +4799,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>370292</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>370292</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>370292</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6679,37 +4817,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119804</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105617</t>
+          <t>106457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131555</t>
+          <t>131554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,45 +4877,10 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>79,19%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>119804</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>105617</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>131555</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>72,12%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>63,58%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>79,19%</t>
         </is>
@@ -6792,37 +4895,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46319</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34568</t>
+          <t>34569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60506</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6857,42 +4960,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>46319</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>34568</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>60506</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -6905,37 +4973,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6969,41 +5037,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7022,37 +5055,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>556</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>574470</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>599865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>547482</t>
+          <t>548207</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>602055</t>
+          <t>599865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,47 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>574470</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>547482</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>602055</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>73,49%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -7135,37 +5133,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>235</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244766</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>219371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217181</t>
+          <t>219371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271754</t>
+          <t>271029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,47 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>244766</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>217181</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>271754</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -7248,37 +5211,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>791</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>819236</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>819236</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>819236</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7312,41 +5275,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>819236</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>819236</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>819236</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7365,37 +5293,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>432</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452968</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>423387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>477134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>425252</t>
+          <t>423387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>477534</t>
+          <t>477134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,47 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>452968</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>425252</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>477534</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>58,18%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>65,33%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -7478,37 +5371,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>277997</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253431</t>
+          <t>253831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>305713</t>
+          <t>307578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,47 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>277997</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>253431</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>305713</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -7591,37 +5449,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>730965</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>730965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>730965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7655,41 +5513,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>730965</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>730965</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>730965</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7708,37 +5531,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513553</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>479745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>550832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>480401</t>
+          <t>479745</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>545914</t>
+          <t>550832</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,47 +5591,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>513553</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>480401</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>545914</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>45,16%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>51,32%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -7821,37 +5609,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>550127</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>512848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>583935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>517766</t>
+          <t>512848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583279</t>
+          <t>583935</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,47 +5669,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>550127</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>517766</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>583279</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>51,72%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>48,68%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>54,84%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -7934,37 +5687,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>976</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1063680</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1063680</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1063680</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7998,41 +5751,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1063680</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1063680</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1063680</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8051,37 +5769,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2233570</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2173571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2292662</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2173249</t>
+          <t>2173571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2291841</t>
+          <t>2292662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,47 +5829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2233570</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2173249</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2291841</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>63,93%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>62,2%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>65,6%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -8164,37 +5847,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1260155</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1201063</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1320154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1201884</t>
+          <t>1201063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1320476</t>
+          <t>1320154</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,47 +5907,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1176</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1260155</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1201884</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1320476</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>34,4%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -8277,37 +5925,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3493725</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3493725</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3493725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8341,41 +5989,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3493725</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3493725</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3493725</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8389,7 +6002,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8397,7 +6010,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -8412,7 +6024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8431,25 +6043,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2023</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2023 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +6065,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8469,17 +6074,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -8550,41 +6144,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -8607,13 +6166,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -8628,37 +6180,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230933</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +6225,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>215956</t>
+          <t>215083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>244322</t>
+          <t>243378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,47 +6240,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>230933</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>215956</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>244322</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>70,09%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>79,29%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -8741,37 +6258,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +6303,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63804</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92170</t>
+          <t>93043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,47 +6318,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>77193</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>63804</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>92170</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>20,71%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>29,91%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -8854,37 +6336,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>477</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308126</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8918,41 +6400,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>308126</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>308126</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>308126</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8971,37 +6418,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>321</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207621</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>219510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195356</t>
+          <t>195523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219976</t>
+          <t>219510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,47 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>207621</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>195356</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>219976</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>71,11%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>80,07%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -9084,37 +6496,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67098</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +6541,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>55209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79363</t>
+          <t>79196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,47 +6556,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>67098</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>54743</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>79363</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -9197,37 +6574,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>429</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274719</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274719</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9261,41 +6638,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>274719</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>274719</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>274719</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9314,37 +6656,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +6701,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64096</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81538</t>
+          <t>82654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,47 +6716,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>73507</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>64096</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>81538</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>54,19%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>68,93%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -9427,37 +6734,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +6779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>35635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54193</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,47 +6794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>36751</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>54193</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>37,86%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>45,81%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -9540,37 +6812,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118289</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118289</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9604,41 +6876,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9657,37 +6894,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358128</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>499868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +6939,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157041</t>
+          <t>150613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>499744</t>
+          <t>499868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,47 +6954,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>358128</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>157041</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>499744</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>47,24%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>65,92%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -9770,37 +6972,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>297</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399957</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +7017,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258341</t>
+          <t>258217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601044</t>
+          <t>607472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,47 +7032,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>399957</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>258341</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>601044</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>52,76%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>34,08%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>79,28%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -9883,37 +7050,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>871</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>758085</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>758085</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>758085</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9947,41 +7114,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>758085</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>758085</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>758085</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10000,37 +7132,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>520</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403893</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>354440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>477798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +7177,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>355946</t>
+          <t>354440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>483100</t>
+          <t>477798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,47 +7192,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>403893</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>355946</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>483100</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>59,9%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>52,79%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>71,65%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -10113,37 +7210,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>270363</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +7255,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191156</t>
+          <t>196458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>318310</t>
+          <t>319816</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,47 +7270,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>270363</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>191156</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>318310</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>40,1%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>28,35%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>47,21%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -10226,37 +7288,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674256</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674256</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10290,41 +7352,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>674256</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>674256</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>674256</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10343,37 +7370,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>452</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>262551</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240761</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>286239</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +7415,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240365</t>
+          <t>240761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>285517</t>
+          <t>286239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,47 +7430,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>262551</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>240365</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>285517</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>42,97%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>39,34%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>46,73%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -10456,37 +7448,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>468</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348486</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324798</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +7493,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>325520</t>
+          <t>324798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370672</t>
+          <t>370276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,47 +7508,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>348486</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>325520</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>370672</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>57,03%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>53,27%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>60,66%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -10569,37 +7526,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>920</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611037</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611037</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611037</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10633,41 +7590,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>611037</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>611037</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>611037</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10686,37 +7608,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1536633</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1214836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1686282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +7653,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1226833</t>
+          <t>1214836</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1693223</t>
+          <t>1686282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,47 +7668,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2367</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1536633</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1226833</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1693223</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>61,69%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -10799,37 +7686,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1207878</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1058229</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1529675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +7731,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1051288</t>
+          <t>1058229</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1517678</t>
+          <t>1529675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,47 +7746,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1537</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1207878</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1051288</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1517678</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -10912,37 +7764,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2744511</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2744511</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2744511</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10976,41 +7828,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3904</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2744511</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2744511</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2744511</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11024,7 +7841,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11032,7 +7849,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P43C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205579</t>
+          <t>206896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236754</t>
+          <t>236523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205579</t>
+          <t>206896</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>236754</t>
+          <t>236523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>65460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96404</t>
+          <t>95087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>65460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96404</t>
+          <t>95087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228930</t>
+          <t>228977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>265036</t>
+          <t>266345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>228930</t>
+          <t>228977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>265036</t>
+          <t>266345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102015</t>
+          <t>100706</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138121</t>
+          <t>138074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102015</t>
+          <t>100706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138121</t>
+          <t>138074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95997</t>
+          <t>96850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120923</t>
+          <t>120282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95997</t>
+          <t>96850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120923</t>
+          <t>120282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46859</t>
+          <t>47500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71785</t>
+          <t>70932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46859</t>
+          <t>47500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71785</t>
+          <t>70932</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>375226</t>
+          <t>374578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>429768</t>
+          <t>426954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>375226</t>
+          <t>374578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>429768</t>
+          <t>426954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>279006</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>333548</t>
+          <t>334196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279006</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333548</t>
+          <t>334196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>285961</t>
+          <t>286868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>335628</t>
+          <t>335353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285961</t>
+          <t>286868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335628</t>
+          <t>335353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>223808</t>
+          <t>224083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273475</t>
+          <t>272568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223808</t>
+          <t>224083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>273475</t>
+          <t>272568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>463813</t>
+          <t>464187</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>533547</t>
+          <t>530331</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>463813</t>
+          <t>464187</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>533547</t>
+          <t>530331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>687403</t>
+          <t>690619</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>757137</t>
+          <t>756763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687403</t>
+          <t>690619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757137</t>
+          <t>756763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1735153</t>
+          <t>1736251</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1849331</t>
+          <t>1846946</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1735153</t>
+          <t>1736251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1849331</t>
+          <t>1846946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1476646</t>
+          <t>1479031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1590824</t>
+          <t>1589726</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1476646</t>
+          <t>1479031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1590824</t>
+          <t>1589726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>240681</t>
+          <t>238472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>268988</t>
+          <t>268894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>240681</t>
+          <t>238472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268988</t>
+          <t>268894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44497</t>
+          <t>44591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72804</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44497</t>
+          <t>44591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72804</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256716</t>
+          <t>256616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285182</t>
+          <t>285670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256716</t>
+          <t>256616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>285182</t>
+          <t>285670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75883</t>
+          <t>75983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75883</t>
+          <t>75983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159825</t>
+          <t>159499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189309</t>
+          <t>190832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159825</t>
+          <t>159499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189309</t>
+          <t>190832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67690</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97174</t>
+          <t>97500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67690</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97174</t>
+          <t>97500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>524173</t>
+          <t>526274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>574476</t>
+          <t>577057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>524173</t>
+          <t>526274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>574476</t>
+          <t>577057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187087</t>
+          <t>184506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237390</t>
+          <t>235289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187087</t>
+          <t>184506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237390</t>
+          <t>235289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>454535</t>
+          <t>454346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>507809</t>
+          <t>507711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>454535</t>
+          <t>454346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>507809</t>
+          <t>507711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246497</t>
+          <t>246595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>299771</t>
+          <t>299960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246497</t>
+          <t>246595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299771</t>
+          <t>299960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>516563</t>
+          <t>515782</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>582654</t>
+          <t>584153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>516563</t>
+          <t>515782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>582654</t>
+          <t>584153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>513533</t>
+          <t>512034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>579624</t>
+          <t>580405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>513533</t>
+          <t>512034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>579624</t>
+          <t>580405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2225757</t>
+          <t>2233972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2341574</t>
+          <t>2348480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2225757</t>
+          <t>2233972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2341574</t>
+          <t>2348480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1173566</t>
+          <t>1166660</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1289383</t>
+          <t>1281168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1173566</t>
+          <t>1166660</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1289383</t>
+          <t>1281168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>255426</t>
+          <t>255030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285371</t>
+          <t>285490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255426</t>
+          <t>255030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285371</t>
+          <t>285490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58059</t>
+          <t>57940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88004</t>
+          <t>88400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58059</t>
+          <t>57940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88004</t>
+          <t>88400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>284941</t>
+          <t>285487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>316335</t>
+          <t>315927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>284941</t>
+          <t>285487</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316335</t>
+          <t>315927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53957</t>
+          <t>54365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>84805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53957</t>
+          <t>54365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>84805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106457</t>
+          <t>106680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131554</t>
+          <t>132698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106457</t>
+          <t>106680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131554</t>
+          <t>132698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>33425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>59443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>33425</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>59443</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>548207</t>
+          <t>544157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>599865</t>
+          <t>600560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>548207</t>
+          <t>544157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>599865</t>
+          <t>600560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>219371</t>
+          <t>218676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271029</t>
+          <t>275079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219371</t>
+          <t>218676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271029</t>
+          <t>275079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>423387</t>
+          <t>424892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>477134</t>
+          <t>480678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>423387</t>
+          <t>424892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>477134</t>
+          <t>480678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>253831</t>
+          <t>250287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>307578</t>
+          <t>306073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253831</t>
+          <t>250287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>307578</t>
+          <t>306073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>479745</t>
+          <t>479633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>550832</t>
+          <t>545760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>479745</t>
+          <t>479633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>550832</t>
+          <t>545760</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>512848</t>
+          <t>517920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>583935</t>
+          <t>584047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>512848</t>
+          <t>517920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583935</t>
+          <t>584047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2173571</t>
+          <t>2180062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2292662</t>
+          <t>2293272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2173571</t>
+          <t>2180062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2292662</t>
+          <t>2293272</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1201063</t>
+          <t>1200453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1320154</t>
+          <t>1313663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1201063</t>
+          <t>1200453</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1320154</t>
+          <t>1313663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -6185,32 +6185,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>230933</t>
+          <t>250586</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215083</t>
+          <t>235249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>243378</t>
+          <t>265693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6220,32 +6220,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>230933</t>
+          <t>250586</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>215083</t>
+          <t>235249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243378</t>
+          <t>265693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -6263,32 +6263,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77193</t>
+          <t>86934</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>71827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93043</t>
+          <t>102271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6298,32 +6298,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77193</t>
+          <t>86934</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>71827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93043</t>
+          <t>102271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>308126</t>
+          <t>337520</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>308126</t>
+          <t>337520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>308126</t>
+          <t>337520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6376,17 +6376,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>308126</t>
+          <t>337520</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>308126</t>
+          <t>337520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>308126</t>
+          <t>337520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195523</t>
+          <t>217237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>219510</t>
+          <t>243004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195523</t>
+          <t>217237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219510</t>
+          <t>243004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -6501,32 +6501,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>77501</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55209</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79196</t>
+          <t>90374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6536,32 +6536,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>77501</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55209</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79196</t>
+          <t>90374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -6579,17 +6579,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>274719</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>274719</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>274719</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>274719</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>274719</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>274719</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6661,32 +6661,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64296</t>
+          <t>71499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82654</t>
+          <t>91029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6696,32 +6696,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64296</t>
+          <t>71499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82654</t>
+          <t>91029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -6739,32 +6739,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>50193</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>40568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53993</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6774,32 +6774,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>50193</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>40568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53993</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -6817,17 +6817,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>131597</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>131597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>131597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>131597</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>131597</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>131597</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6899,32 +6899,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>358128</t>
+          <t>397476</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150613</t>
+          <t>376978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>499868</t>
+          <t>417977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6934,32 +6934,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>358128</t>
+          <t>397476</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150613</t>
+          <t>376978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>499868</t>
+          <t>417977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -6977,32 +6977,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>399957</t>
+          <t>219242</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258217</t>
+          <t>198741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607472</t>
+          <t>239740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7012,32 +7012,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>399957</t>
+          <t>219242</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258217</t>
+          <t>198741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607472</t>
+          <t>239740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -7055,17 +7055,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>758085</t>
+          <t>616718</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>758085</t>
+          <t>616718</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>758085</t>
+          <t>616718</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7090,17 +7090,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>758085</t>
+          <t>616718</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>758085</t>
+          <t>616718</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>758085</t>
+          <t>616718</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7137,32 +7137,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>403893</t>
+          <t>326666</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>354440</t>
+          <t>305091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>477798</t>
+          <t>346868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7172,32 +7172,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>403893</t>
+          <t>326666</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354440</t>
+          <t>305091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>477798</t>
+          <t>346868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -7215,32 +7215,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>270363</t>
+          <t>313392</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196458</t>
+          <t>293190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319816</t>
+          <t>334967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7250,32 +7250,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>270363</t>
+          <t>313392</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196458</t>
+          <t>293190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319816</t>
+          <t>334967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>674256</t>
+          <t>640058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>674256</t>
+          <t>640058</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>674256</t>
+          <t>640058</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7328,17 +7328,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>674256</t>
+          <t>640058</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>674256</t>
+          <t>640058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>674256</t>
+          <t>640058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7375,32 +7375,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>262551</t>
+          <t>284273</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>240761</t>
+          <t>260813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>286239</t>
+          <t>310697</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7410,32 +7410,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>262551</t>
+          <t>284273</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240761</t>
+          <t>260813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>286239</t>
+          <t>310697</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -7453,32 +7453,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>348486</t>
+          <t>391223</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324798</t>
+          <t>364799</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>370276</t>
+          <t>414683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7488,32 +7488,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>348486</t>
+          <t>391223</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>324798</t>
+          <t>364799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370276</t>
+          <t>414683</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>611037</t>
+          <t>675496</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>611037</t>
+          <t>675496</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>611037</t>
+          <t>675496</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>611037</t>
+          <t>675496</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>611037</t>
+          <t>675496</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>611037</t>
+          <t>675496</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7613,32 +7613,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1536633</t>
+          <t>1570516</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1214836</t>
+          <t>1515550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1686282</t>
+          <t>1614339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7648,32 +7648,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1536633</t>
+          <t>1570516</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1214836</t>
+          <t>1515550</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1686282</t>
+          <t>1614339</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -7691,32 +7691,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1207878</t>
+          <t>1138484</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1058229</t>
+          <t>1094661</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1529675</t>
+          <t>1193450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7726,32 +7726,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1207878</t>
+          <t>1138484</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1058229</t>
+          <t>1094661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1529675</t>
+          <t>1193450</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -7769,17 +7769,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2744511</t>
+          <t>2709000</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2744511</t>
+          <t>2709000</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2744511</t>
+          <t>2709000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7804,17 +7804,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2744511</t>
+          <t>2709000</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2744511</t>
+          <t>2709000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2744511</t>
+          <t>2709000</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
